--- a/Data/2016_F013B4_CO_ITR/2016_F013B4_CO_ITR_SoilAnalysis.xlsx
+++ b/Data/2016_F013B4_CO_ITR/2016_F013B4_CO_ITR_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2016_F013B4_CO_ITR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FC5A9C-E34D-426C-9E15-48291786B73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BE2BDF-CC18-4E17-977A-6A5E8423D1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1665" yWindow="-26070" windowWidth="27270" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -812,9 +812,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1518,6 +1515,9 @@
   </si>
   <si>
     <t>2016-p01-1</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -2357,13 +2357,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -2374,7 +2374,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C2">
         <v>408957.18540000002</v>
@@ -2391,7 +2391,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C3">
         <v>408962.41840000002</v>
@@ -2408,7 +2408,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C4">
         <v>408956.30570000003</v>
@@ -2425,7 +2425,7 @@
         <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C5">
         <v>408961.93680000002</v>
@@ -2442,7 +2442,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C6">
         <v>408955.91499999899</v>
@@ -2459,7 +2459,7 @@
         <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C7">
         <v>408960.96830000001</v>
@@ -2476,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C8">
         <v>408955.01179999899</v>
@@ -2493,7 +2493,7 @@
         <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C9">
         <v>408960.493599999</v>
@@ -2510,7 +2510,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C10">
         <v>408928.783999999</v>
@@ -2527,7 +2527,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C11">
         <v>408927.88109999901</v>
@@ -2544,7 +2544,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C12">
         <v>408927.42930000002</v>
@@ -2561,7 +2561,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C13">
         <v>408926.557299999</v>
@@ -2578,7 +2578,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C14">
         <v>408845.46089999902</v>
@@ -2595,7 +2595,7 @@
         <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C15">
         <v>408850.18070000003</v>
@@ -2612,7 +2612,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C16">
         <v>408844.56319999899</v>
@@ -2629,7 +2629,7 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C17">
         <v>408849.70020000002</v>
@@ -2646,7 +2646,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C18">
         <v>408844.13500000001</v>
@@ -2663,7 +2663,7 @@
         <v>159</v>
       </c>
       <c r="B19" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C19">
         <v>408848.73200000002</v>
@@ -2680,7 +2680,7 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C20">
         <v>408843.26179999899</v>
@@ -2697,7 +2697,7 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21">
         <v>408848.231299999</v>
@@ -2714,7 +2714,7 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C22">
         <v>408817.00829999999</v>
@@ -2731,7 +2731,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C23">
         <v>408816.12689999898</v>
@@ -2748,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C24">
         <v>408815.666399999</v>
@@ -2765,7 +2765,7 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C25">
         <v>408814.80080000003</v>
@@ -2782,7 +2782,7 @@
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C26">
         <v>408788.581799999</v>
@@ -2799,7 +2799,7 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C27">
         <v>408793.35800000001</v>
@@ -2816,7 +2816,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C28">
         <v>408787.67560000002</v>
@@ -2833,7 +2833,7 @@
         <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C29">
         <v>408792.866099999</v>
@@ -2850,7 +2850,7 @@
         <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C30">
         <v>408787.222799999</v>
@@ -2867,7 +2867,7 @@
         <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C31">
         <v>408791.8947</v>
@@ -2884,7 +2884,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C32">
         <v>408786.36930000002</v>
@@ -2901,7 +2901,7 @@
         <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C33">
         <v>408791.43050000002</v>
@@ -2918,7 +2918,7 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C34">
         <v>408760.11839999899</v>
@@ -2935,7 +2935,7 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C35">
         <v>408759.24219999899</v>
@@ -2952,7 +2952,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C36">
         <v>408758.807399999</v>
@@ -2969,7 +2969,7 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C37">
         <v>408757.90980000002</v>
@@ -2986,7 +2986,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3003,7 +3003,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3020,7 +3020,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3037,7 +3037,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3054,7 +3054,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3071,7 +3071,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3088,7 +3088,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3105,7 +3105,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3122,7 +3122,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3139,7 +3139,7 @@
         <v>72</v>
       </c>
       <c r="B47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47">
         <v>408747.36800000002</v>
@@ -3156,7 +3156,7 @@
         <v>77</v>
       </c>
       <c r="B48" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C48">
         <v>408741.31040000002</v>
@@ -3173,7 +3173,7 @@
         <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49">
         <v>408741.583099999</v>
@@ -3190,7 +3190,7 @@
         <v>73</v>
       </c>
       <c r="B50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C50">
         <v>408747.01990000001</v>
@@ -3207,7 +3207,7 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C51">
         <v>408746.78700000001</v>
@@ -3224,7 +3224,7 @@
         <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C52">
         <v>408740.70369999902</v>
@@ -3241,7 +3241,7 @@
         <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C53">
         <v>408740.96580000001</v>
@@ -3258,7 +3258,7 @@
         <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C54">
         <v>408734.69020000001</v>
@@ -3275,7 +3275,7 @@
         <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C55">
         <v>408734.44760000001</v>
@@ -3292,7 +3292,7 @@
         <v>97</v>
       </c>
       <c r="B56" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C56">
         <v>408728.347899999</v>
@@ -3309,7 +3309,7 @@
         <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C57">
         <v>408728.57990000001</v>
@@ -3326,7 +3326,7 @@
         <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C58">
         <v>408734.16200000001</v>
@@ -3343,7 +3343,7 @@
         <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C59">
         <v>408733.81439999898</v>
@@ -3360,7 +3360,7 @@
         <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C60">
         <v>408727.74089999998</v>
@@ -3377,7 +3377,7 @@
         <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C61">
         <v>408727.98920000001</v>
@@ -3394,7 +3394,7 @@
         <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C62">
         <v>408733.443499999</v>
@@ -3411,7 +3411,7 @@
         <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C63">
         <v>408733.15990000003</v>
@@ -3428,7 +3428,7 @@
         <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C64">
         <v>408727.05959999899</v>
@@ -3445,7 +3445,7 @@
         <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C65">
         <v>408727.3763</v>
@@ -3462,7 +3462,7 @@
         <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C66">
         <v>408732.84250000003</v>
@@ -3479,7 +3479,7 @@
         <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C67">
         <v>408732.57250000001</v>
@@ -3496,7 +3496,7 @@
         <v>91</v>
       </c>
       <c r="B68" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C68">
         <v>408726.50510000001</v>
@@ -3513,7 +3513,7 @@
         <v>92</v>
       </c>
       <c r="B69" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C69">
         <v>408726.75140000001</v>
@@ -3530,7 +3530,7 @@
         <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C70">
         <v>408720.46580000001</v>
@@ -3547,7 +3547,7 @@
         <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C71">
         <v>408720.19679999899</v>
@@ -3564,7 +3564,7 @@
         <v>113</v>
       </c>
       <c r="B72" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C72">
         <v>408714.09700000001</v>
@@ -3581,7 +3581,7 @@
         <v>114</v>
       </c>
       <c r="B73" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C73">
         <v>408714.40309999901</v>
@@ -3598,7 +3598,7 @@
         <v>101</v>
       </c>
       <c r="B74" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C74">
         <v>408719.8885</v>
@@ -3615,7 +3615,7 @@
         <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C75">
         <v>408719.60830000002</v>
@@ -3632,7 +3632,7 @@
         <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C76">
         <v>408713.53340000001</v>
@@ -3649,7 +3649,7 @@
         <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C77">
         <v>408713.790299999</v>
@@ -3666,7 +3666,7 @@
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C78">
         <v>408719.22999999899</v>
@@ -3683,7 +3683,7 @@
         <v>104</v>
       </c>
       <c r="B79" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C79">
         <v>408718.943499999</v>
@@ -3700,7 +3700,7 @@
         <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C80">
         <v>408712.91200000001</v>
@@ -3717,7 +3717,7 @@
         <v>110</v>
       </c>
       <c r="B81" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C81">
         <v>408713.13880000002</v>
@@ -3734,7 +3734,7 @@
         <v>105</v>
       </c>
       <c r="B82" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C82">
         <v>408718.61729999899</v>
@@ -3751,7 +3751,7 @@
         <v>106</v>
       </c>
       <c r="B83" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C83">
         <v>408718.331899999</v>
@@ -3768,7 +3768,7 @@
         <v>107</v>
       </c>
       <c r="B84" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C84">
         <v>408712.24329999898</v>
@@ -3785,7 +3785,7 @@
         <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C85">
         <v>408712.455599999</v>
@@ -3802,7 +3802,7 @@
         <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C86">
         <v>408706.2476</v>
@@ -3819,7 +3819,7 @@
         <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C87">
         <v>408705.94109999901</v>
@@ -3836,7 +3836,7 @@
         <v>129</v>
       </c>
       <c r="B88" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C88">
         <v>408699.85230000003</v>
@@ -3853,7 +3853,7 @@
         <v>130</v>
       </c>
       <c r="B89" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C89">
         <v>408700.13030000002</v>
@@ -3870,7 +3870,7 @@
         <v>117</v>
       </c>
       <c r="B90" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C90">
         <v>408705.62539999897</v>
@@ -3887,7 +3887,7 @@
         <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C91">
         <v>408705.38500000001</v>
@@ -3904,7 +3904,7 @@
         <v>127</v>
       </c>
       <c r="B92" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C92">
         <v>408699.26530000003</v>
@@ -3921,7 +3921,7 @@
         <v>128</v>
       </c>
       <c r="B93" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C93">
         <v>408699.535299999</v>
@@ -3938,7 +3938,7 @@
         <v>119</v>
       </c>
       <c r="B94" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C94">
         <v>408704.99829999899</v>
@@ -3955,7 +3955,7 @@
         <v>120</v>
       </c>
       <c r="B95" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C95">
         <v>408704.72440000001</v>
@@ -3972,7 +3972,7 @@
         <v>125</v>
       </c>
       <c r="B96" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C96">
         <v>408698.68780000001</v>
@@ -3989,7 +3989,7 @@
         <v>126</v>
       </c>
       <c r="B97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C97">
         <v>408698.93699999899</v>
@@ -4006,7 +4006,7 @@
         <v>121</v>
       </c>
       <c r="B98" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C98">
         <v>408704.38349999901</v>
@@ -4023,7 +4023,7 @@
         <v>122</v>
       </c>
       <c r="B99" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C99">
         <v>408704.0895</v>
@@ -4040,7 +4040,7 @@
         <v>123</v>
       </c>
       <c r="B100" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C100">
         <v>408697.99089999899</v>
@@ -4057,7 +4057,7 @@
         <v>124</v>
       </c>
       <c r="B101" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C101">
         <v>408698.26829999901</v>
@@ -4084,13 +4084,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C2">
         <v>408957.29330000002</v>
@@ -4118,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C3">
         <v>408956.69130000001</v>
@@ -4135,7 +4135,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C4">
         <v>408956.084399999</v>
@@ -4152,7 +4152,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C5">
         <v>408955.49589999899</v>
@@ -4169,7 +4169,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C6">
         <v>408943.05879999901</v>
@@ -4186,7 +4186,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C7">
         <v>408942.48519999901</v>
@@ -4203,7 +4203,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C8">
         <v>408941.846599999</v>
@@ -4220,7 +4220,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C9">
         <v>408941.274299999</v>
@@ -4237,7 +4237,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C10">
         <v>408928.85560000001</v>
@@ -4254,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C11">
         <v>408928.25300000003</v>
@@ -4271,7 +4271,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C12">
         <v>408927.64370000002</v>
@@ -4288,7 +4288,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C13">
         <v>408927.035299999</v>
@@ -4305,7 +4305,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C14">
         <v>408914.35340000002</v>
@@ -4322,7 +4322,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C15">
         <v>408913.7599</v>
@@ -4339,7 +4339,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C16">
         <v>408913.14380000002</v>
@@ -4356,7 +4356,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C17">
         <v>408912.52870000002</v>
@@ -4373,7 +4373,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C18">
         <v>408859.25290000002</v>
@@ -4390,7 +4390,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C19">
         <v>408858.64659999899</v>
@@ -4407,7 +4407,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C20">
         <v>408858.0344</v>
@@ -4424,7 +4424,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C21">
         <v>408857.44079999899</v>
@@ -4441,7 +4441,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C22">
         <v>408845.03460000001</v>
@@ -4458,7 +4458,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C23">
         <v>408844.4375</v>
@@ -4475,7 +4475,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C24">
         <v>408843.829399999</v>
@@ -4492,7 +4492,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C25">
         <v>408843.20490000001</v>
@@ -4509,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C26">
         <v>408830.81489999901</v>
@@ -4526,7 +4526,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C27">
         <v>408830.206899999</v>
@@ -4543,7 +4543,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C28">
         <v>408829.59519999899</v>
@@ -4560,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C29">
         <v>408828.99920000002</v>
@@ -4577,7 +4577,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C30">
         <v>408816.59179999901</v>
@@ -4594,7 +4594,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C31">
         <v>408815.986199999</v>
@@ -4611,7 +4611,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C32">
         <v>408815.39</v>
@@ -4628,7 +4628,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C33">
         <v>408814.777</v>
@@ -4645,7 +4645,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C34">
         <v>408802.449499999</v>
@@ -4662,7 +4662,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C35">
         <v>408801.83819999901</v>
@@ -4679,7 +4679,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C36">
         <v>408801.21379999898</v>
@@ -4696,7 +4696,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C37">
         <v>408800.62819999899</v>
@@ -4713,7 +4713,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C38">
         <v>408788.22350000002</v>
@@ -4730,7 +4730,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C39">
         <v>408787.60700000002</v>
@@ -4747,7 +4747,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C40">
         <v>408787.00040000002</v>
@@ -4764,7 +4764,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C41">
         <v>408786.40159999899</v>
@@ -4781,7 +4781,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C42">
         <v>408773.99790000002</v>
@@ -4798,7 +4798,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C43">
         <v>408773.39649999898</v>
@@ -4815,7 +4815,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C44">
         <v>408772.784099999</v>
@@ -4832,7 +4832,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C45">
         <v>408772.17050000001</v>
@@ -4849,7 +4849,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C46">
         <v>408759.7758</v>
@@ -4866,7 +4866,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C47">
         <v>408759.1692</v>
@@ -4883,7 +4883,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C48">
         <v>408758.57179999899</v>
@@ -4900,7 +4900,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C49">
         <v>408757.959299999</v>
@@ -4917,7 +4917,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C50">
         <v>408745.63719999901</v>
@@ -4934,7 +4934,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C51">
         <v>408745.02610000002</v>
@@ -4951,7 +4951,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C52">
         <v>408744.41419999901</v>
@@ -4968,7 +4968,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C53">
         <v>408743.81449999899</v>
@@ -4985,7 +4985,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C54">
         <v>408731.41739999899</v>
@@ -5002,7 +5002,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C55">
         <v>408730.80660000001</v>
@@ -5019,7 +5019,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C56">
         <v>408730.19</v>
@@ -5036,7 +5036,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C57">
         <v>408729.61050000001</v>
@@ -5053,7 +5053,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C58">
         <v>408717.2047</v>
@@ -5070,7 +5070,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C59">
         <v>408716.59240000002</v>
@@ -5087,7 +5087,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C60">
         <v>408715.98029999901</v>
@@ -5104,7 +5104,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C61">
         <v>408715.38030000002</v>
@@ -5121,7 +5121,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C62">
         <v>408702.95299999899</v>
@@ -5138,7 +5138,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C63">
         <v>408702.35950000002</v>
@@ -5155,7 +5155,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C64">
         <v>408701.76500000001</v>
@@ -5172,7 +5172,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C65">
         <v>408701.14669999899</v>
@@ -5202,211 +5202,211 @@
         <v>192</v>
       </c>
       <c r="C1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>282</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>283</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>284</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>285</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>286</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>287</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>288</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>289</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>291</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>292</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>293</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>294</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>295</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>296</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>297</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>298</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>299</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>300</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>301</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>302</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>303</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>304</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>305</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>306</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>307</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>308</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>309</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>310</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>311</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>313</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>314</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>315</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>316</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>317</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>318</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>319</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>320</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>321</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>322</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>323</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>324</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>325</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>326</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -45885,211 +45885,211 @@
         <v>258</v>
       </c>
       <c r="C1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>282</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>283</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>284</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>285</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>286</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>287</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>288</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>289</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>291</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>292</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>293</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>294</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>295</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>296</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>297</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>298</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>299</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>300</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>301</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>302</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>303</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>304</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>305</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>306</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>307</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>308</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>309</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>310</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>311</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>313</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>314</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>315</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>316</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>317</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>318</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>319</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>320</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>321</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>322</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>323</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>324</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>325</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>326</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">

--- a/Data/2016_F013B4_CO_ITR/2016_F013B4_CO_ITR_SoilAnalysis.xlsx
+++ b/Data/2016_F013B4_CO_ITR/2016_F013B4_CO_ITR_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2016_F013B4_CO_ITR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB5CA3B-71E0-469E-833F-365C4422E6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487DCC4F-D720-4ECA-84CA-19FBB591D3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1530" yWindow="-24735" windowWidth="17775" windowHeight="24285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1815" yWindow="-24900" windowWidth="16335" windowHeight="23370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -812,12 +812,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1518,6 +1512,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -2357,13 +2357,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -2374,7 +2374,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C2">
         <v>408957.18540000002</v>
@@ -2391,7 +2391,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C3">
         <v>408962.41840000002</v>
@@ -2408,7 +2408,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C4">
         <v>408956.30570000003</v>
@@ -2425,7 +2425,7 @@
         <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C5">
         <v>408961.93680000002</v>
@@ -2442,7 +2442,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C6">
         <v>408955.91499999899</v>
@@ -2459,7 +2459,7 @@
         <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C7">
         <v>408960.96830000001</v>
@@ -2476,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C8">
         <v>408955.01179999899</v>
@@ -2493,7 +2493,7 @@
         <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C9">
         <v>408960.493599999</v>
@@ -2510,7 +2510,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C10">
         <v>408928.783999999</v>
@@ -2527,7 +2527,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C11">
         <v>408927.88109999901</v>
@@ -2544,7 +2544,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C12">
         <v>408927.42930000002</v>
@@ -2561,7 +2561,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C13">
         <v>408926.557299999</v>
@@ -2578,7 +2578,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C14">
         <v>408845.46089999902</v>
@@ -2595,7 +2595,7 @@
         <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C15">
         <v>408850.18070000003</v>
@@ -2612,7 +2612,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C16">
         <v>408844.56319999899</v>
@@ -2629,7 +2629,7 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C17">
         <v>408849.70020000002</v>
@@ -2646,7 +2646,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C18">
         <v>408844.13500000001</v>
@@ -2663,7 +2663,7 @@
         <v>159</v>
       </c>
       <c r="B19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C19">
         <v>408848.73200000002</v>
@@ -2680,7 +2680,7 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C20">
         <v>408843.26179999899</v>
@@ -2697,7 +2697,7 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C21">
         <v>408848.231299999</v>
@@ -2714,7 +2714,7 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C22">
         <v>408817.00829999999</v>
@@ -2731,7 +2731,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C23">
         <v>408816.12689999898</v>
@@ -2748,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C24">
         <v>408815.666399999</v>
@@ -2765,7 +2765,7 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C25">
         <v>408814.80080000003</v>
@@ -2782,7 +2782,7 @@
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C26">
         <v>408788.581799999</v>
@@ -2799,7 +2799,7 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C27">
         <v>408793.35800000001</v>
@@ -2816,7 +2816,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C28">
         <v>408787.67560000002</v>
@@ -2833,7 +2833,7 @@
         <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C29">
         <v>408792.866099999</v>
@@ -2850,7 +2850,7 @@
         <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C30">
         <v>408787.222799999</v>
@@ -2867,7 +2867,7 @@
         <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C31">
         <v>408791.8947</v>
@@ -2884,7 +2884,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C32">
         <v>408786.36930000002</v>
@@ -2901,7 +2901,7 @@
         <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C33">
         <v>408791.43050000002</v>
@@ -2918,7 +2918,7 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C34">
         <v>408760.11839999899</v>
@@ -2935,7 +2935,7 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C35">
         <v>408759.24219999899</v>
@@ -2952,7 +2952,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C36">
         <v>408758.807399999</v>
@@ -2969,7 +2969,7 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C37">
         <v>408757.90980000002</v>
@@ -2986,7 +2986,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3003,7 +3003,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3020,7 +3020,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3037,7 +3037,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3054,7 +3054,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3071,7 +3071,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3088,7 +3088,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3105,7 +3105,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3122,7 +3122,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3139,7 +3139,7 @@
         <v>72</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C47">
         <v>408747.36800000002</v>
@@ -3156,7 +3156,7 @@
         <v>77</v>
       </c>
       <c r="B48" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C48">
         <v>408741.31040000002</v>
@@ -3173,7 +3173,7 @@
         <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C49">
         <v>408741.583099999</v>
@@ -3190,7 +3190,7 @@
         <v>73</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C50">
         <v>408747.01990000001</v>
@@ -3207,7 +3207,7 @@
         <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C51">
         <v>408746.78700000001</v>
@@ -3224,7 +3224,7 @@
         <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C52">
         <v>408740.70369999902</v>
@@ -3241,7 +3241,7 @@
         <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C53">
         <v>408740.96580000001</v>
@@ -3258,7 +3258,7 @@
         <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C54">
         <v>408734.69020000001</v>
@@ -3275,7 +3275,7 @@
         <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C55">
         <v>408734.44760000001</v>
@@ -3292,7 +3292,7 @@
         <v>97</v>
       </c>
       <c r="B56" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C56">
         <v>408728.347899999</v>
@@ -3309,7 +3309,7 @@
         <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C57">
         <v>408728.57990000001</v>
@@ -3326,7 +3326,7 @@
         <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C58">
         <v>408734.16200000001</v>
@@ -3343,7 +3343,7 @@
         <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C59">
         <v>408733.81439999898</v>
@@ -3360,7 +3360,7 @@
         <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C60">
         <v>408727.74089999998</v>
@@ -3377,7 +3377,7 @@
         <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C61">
         <v>408727.98920000001</v>
@@ -3394,7 +3394,7 @@
         <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C62">
         <v>408733.443499999</v>
@@ -3411,7 +3411,7 @@
         <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C63">
         <v>408733.15990000003</v>
@@ -3428,7 +3428,7 @@
         <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C64">
         <v>408727.05959999899</v>
@@ -3445,7 +3445,7 @@
         <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C65">
         <v>408727.3763</v>
@@ -3462,7 +3462,7 @@
         <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C66">
         <v>408732.84250000003</v>
@@ -3479,7 +3479,7 @@
         <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C67">
         <v>408732.57250000001</v>
@@ -3496,7 +3496,7 @@
         <v>91</v>
       </c>
       <c r="B68" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C68">
         <v>408726.50510000001</v>
@@ -3513,7 +3513,7 @@
         <v>92</v>
       </c>
       <c r="B69" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C69">
         <v>408726.75140000001</v>
@@ -3530,7 +3530,7 @@
         <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C70">
         <v>408720.46580000001</v>
@@ -3547,7 +3547,7 @@
         <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C71">
         <v>408720.19679999899</v>
@@ -3564,7 +3564,7 @@
         <v>113</v>
       </c>
       <c r="B72" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C72">
         <v>408714.09700000001</v>
@@ -3581,7 +3581,7 @@
         <v>114</v>
       </c>
       <c r="B73" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C73">
         <v>408714.40309999901</v>
@@ -3598,7 +3598,7 @@
         <v>101</v>
       </c>
       <c r="B74" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C74">
         <v>408719.8885</v>
@@ -3615,7 +3615,7 @@
         <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C75">
         <v>408719.60830000002</v>
@@ -3632,7 +3632,7 @@
         <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C76">
         <v>408713.53340000001</v>
@@ -3649,7 +3649,7 @@
         <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C77">
         <v>408713.790299999</v>
@@ -3666,7 +3666,7 @@
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C78">
         <v>408719.22999999899</v>
@@ -3683,7 +3683,7 @@
         <v>104</v>
       </c>
       <c r="B79" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C79">
         <v>408718.943499999</v>
@@ -3700,7 +3700,7 @@
         <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C80">
         <v>408712.91200000001</v>
@@ -3717,7 +3717,7 @@
         <v>110</v>
       </c>
       <c r="B81" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C81">
         <v>408713.13880000002</v>
@@ -3734,7 +3734,7 @@
         <v>105</v>
       </c>
       <c r="B82" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C82">
         <v>408718.61729999899</v>
@@ -3751,7 +3751,7 @@
         <v>106</v>
       </c>
       <c r="B83" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C83">
         <v>408718.331899999</v>
@@ -3768,7 +3768,7 @@
         <v>107</v>
       </c>
       <c r="B84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C84">
         <v>408712.24329999898</v>
@@ -3785,7 +3785,7 @@
         <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C85">
         <v>408712.455599999</v>
@@ -3802,7 +3802,7 @@
         <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C86">
         <v>408706.2476</v>
@@ -3819,7 +3819,7 @@
         <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C87">
         <v>408705.94109999901</v>
@@ -3836,7 +3836,7 @@
         <v>129</v>
       </c>
       <c r="B88" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C88">
         <v>408699.85230000003</v>
@@ -3853,7 +3853,7 @@
         <v>130</v>
       </c>
       <c r="B89" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C89">
         <v>408700.13030000002</v>
@@ -3870,7 +3870,7 @@
         <v>117</v>
       </c>
       <c r="B90" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C90">
         <v>408705.62539999897</v>
@@ -3887,7 +3887,7 @@
         <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C91">
         <v>408705.38500000001</v>
@@ -3904,7 +3904,7 @@
         <v>127</v>
       </c>
       <c r="B92" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C92">
         <v>408699.26530000003</v>
@@ -3921,7 +3921,7 @@
         <v>128</v>
       </c>
       <c r="B93" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C93">
         <v>408699.535299999</v>
@@ -3938,7 +3938,7 @@
         <v>119</v>
       </c>
       <c r="B94" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C94">
         <v>408704.99829999899</v>
@@ -3955,7 +3955,7 @@
         <v>120</v>
       </c>
       <c r="B95" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C95">
         <v>408704.72440000001</v>
@@ -3972,7 +3972,7 @@
         <v>125</v>
       </c>
       <c r="B96" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C96">
         <v>408698.68780000001</v>
@@ -3989,7 +3989,7 @@
         <v>126</v>
       </c>
       <c r="B97" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C97">
         <v>408698.93699999899</v>
@@ -4006,7 +4006,7 @@
         <v>121</v>
       </c>
       <c r="B98" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C98">
         <v>408704.38349999901</v>
@@ -4023,7 +4023,7 @@
         <v>122</v>
       </c>
       <c r="B99" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C99">
         <v>408704.0895</v>
@@ -4040,7 +4040,7 @@
         <v>123</v>
       </c>
       <c r="B100" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C100">
         <v>408697.99089999899</v>
@@ -4057,7 +4057,7 @@
         <v>124</v>
       </c>
       <c r="B101" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C101">
         <v>408698.26829999901</v>
@@ -4084,13 +4084,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -4101,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C2">
         <v>408957.29330000002</v>
@@ -4118,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C3">
         <v>408956.69130000001</v>
@@ -4135,7 +4135,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C4">
         <v>408956.084399999</v>
@@ -4152,7 +4152,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C5">
         <v>408955.49589999899</v>
@@ -4169,7 +4169,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C6">
         <v>408943.05879999901</v>
@@ -4186,7 +4186,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C7">
         <v>408942.48519999901</v>
@@ -4203,7 +4203,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C8">
         <v>408941.846599999</v>
@@ -4220,7 +4220,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C9">
         <v>408941.274299999</v>
@@ -4237,7 +4237,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C10">
         <v>408928.85560000001</v>
@@ -4254,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C11">
         <v>408928.25300000003</v>
@@ -4271,7 +4271,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C12">
         <v>408927.64370000002</v>
@@ -4288,7 +4288,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C13">
         <v>408927.035299999</v>
@@ -4305,7 +4305,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C14">
         <v>408914.35340000002</v>
@@ -4322,7 +4322,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C15">
         <v>408913.7599</v>
@@ -4339,7 +4339,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C16">
         <v>408913.14380000002</v>
@@ -4356,7 +4356,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C17">
         <v>408912.52870000002</v>
@@ -4373,7 +4373,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C18">
         <v>408859.25290000002</v>
@@ -4390,7 +4390,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C19">
         <v>408858.64659999899</v>
@@ -4407,7 +4407,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C20">
         <v>408858.0344</v>
@@ -4424,7 +4424,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C21">
         <v>408857.44079999899</v>
@@ -4441,7 +4441,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C22">
         <v>408845.03460000001</v>
@@ -4458,7 +4458,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C23">
         <v>408844.4375</v>
@@ -4475,7 +4475,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C24">
         <v>408843.829399999</v>
@@ -4492,7 +4492,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C25">
         <v>408843.20490000001</v>
@@ -4509,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C26">
         <v>408830.81489999901</v>
@@ -4526,7 +4526,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C27">
         <v>408830.206899999</v>
@@ -4543,7 +4543,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C28">
         <v>408829.59519999899</v>
@@ -4560,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C29">
         <v>408828.99920000002</v>
@@ -4577,7 +4577,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C30">
         <v>408816.59179999901</v>
@@ -4594,7 +4594,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C31">
         <v>408815.986199999</v>
@@ -4611,7 +4611,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C32">
         <v>408815.39</v>
@@ -4628,7 +4628,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C33">
         <v>408814.777</v>
@@ -4645,7 +4645,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C34">
         <v>408802.449499999</v>
@@ -4662,7 +4662,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C35">
         <v>408801.83819999901</v>
@@ -4679,7 +4679,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C36">
         <v>408801.21379999898</v>
@@ -4696,7 +4696,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C37">
         <v>408800.62819999899</v>
@@ -4713,7 +4713,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C38">
         <v>408788.22350000002</v>
@@ -4730,7 +4730,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C39">
         <v>408787.60700000002</v>
@@ -4747,7 +4747,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C40">
         <v>408787.00040000002</v>
@@ -4764,7 +4764,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C41">
         <v>408786.40159999899</v>
@@ -4781,7 +4781,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C42">
         <v>408773.99790000002</v>
@@ -4798,7 +4798,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C43">
         <v>408773.39649999898</v>
@@ -4815,7 +4815,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C44">
         <v>408772.784099999</v>
@@ -4832,7 +4832,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C45">
         <v>408772.17050000001</v>
@@ -4849,7 +4849,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C46">
         <v>408759.7758</v>
@@ -4866,7 +4866,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C47">
         <v>408759.1692</v>
@@ -4883,7 +4883,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C48">
         <v>408758.57179999899</v>
@@ -4900,7 +4900,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C49">
         <v>408757.959299999</v>
@@ -4917,7 +4917,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C50">
         <v>408745.63719999901</v>
@@ -4934,7 +4934,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C51">
         <v>408745.02610000002</v>
@@ -4951,7 +4951,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C52">
         <v>408744.41419999901</v>
@@ -4968,7 +4968,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C53">
         <v>408743.81449999899</v>
@@ -4985,7 +4985,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C54">
         <v>408731.41739999899</v>
@@ -5002,7 +5002,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C55">
         <v>408730.80660000001</v>
@@ -5019,7 +5019,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C56">
         <v>408730.19</v>
@@ -5036,7 +5036,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C57">
         <v>408729.61050000001</v>
@@ -5053,7 +5053,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C58">
         <v>408717.2047</v>
@@ -5070,7 +5070,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C59">
         <v>408716.59240000002</v>
@@ -5087,7 +5087,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C60">
         <v>408715.98029999901</v>
@@ -5104,7 +5104,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C61">
         <v>408715.38030000002</v>
@@ -5121,7 +5121,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C62">
         <v>408702.95299999899</v>
@@ -5138,7 +5138,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C63">
         <v>408702.35950000002</v>
@@ -5155,7 +5155,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C64">
         <v>408701.76500000001</v>
@@ -5172,7 +5172,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C65">
         <v>408701.14669999899</v>
@@ -5202,211 +5202,211 @@
         <v>192</v>
       </c>
       <c r="C1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1" t="s">
         <v>494</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>291</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>292</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>293</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>294</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>295</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>296</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>297</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>298</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>299</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>300</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>301</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>302</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>303</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>304</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>305</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>306</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>307</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>308</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>309</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>311</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>312</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>313</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>314</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>315</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>316</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>317</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>318</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>319</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>320</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>321</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>322</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>323</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>324</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>325</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -45885,211 +45885,211 @@
         <v>258</v>
       </c>
       <c r="C1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1" t="s">
         <v>494</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>291</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>292</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>293</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>294</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>295</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>296</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>297</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>298</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>299</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>300</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>301</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>302</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>303</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>304</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>305</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>306</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>307</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>308</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>309</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>311</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>312</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>313</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>314</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>315</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>316</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>317</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>318</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>319</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>320</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>321</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>322</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>323</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>324</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>325</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
